--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F4CD37-1B0B-44EA-AB20-0734B15BDED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="154">
   <si>
     <t>Documento</t>
   </si>
@@ -82,12 +76,267 @@
     <t>048008</t>
   </si>
   <si>
-    <t>XYZ999</t>
+    <t>COT200001</t>
+  </si>
+  <si>
+    <t>048101</t>
+  </si>
+  <si>
+    <t>COT200002</t>
+  </si>
+  <si>
+    <t>048102</t>
+  </si>
+  <si>
+    <t>COT200003</t>
+  </si>
+  <si>
+    <t>048103</t>
+  </si>
+  <si>
+    <t>COT200004</t>
+  </si>
+  <si>
+    <t>048104</t>
+  </si>
+  <si>
+    <t>COT200005</t>
+  </si>
+  <si>
+    <t>048105</t>
+  </si>
+  <si>
+    <t>COT200006</t>
+  </si>
+  <si>
+    <t>048106</t>
+  </si>
+  <si>
+    <t>COT200007</t>
+  </si>
+  <si>
+    <t>048107</t>
+  </si>
+  <si>
+    <t>COT200008</t>
+  </si>
+  <si>
+    <t>048108</t>
+  </si>
+  <si>
+    <t>COT200009</t>
+  </si>
+  <si>
+    <t>048109</t>
+  </si>
+  <si>
+    <t>COT200010</t>
+  </si>
+  <si>
+    <t>048110</t>
+  </si>
+  <si>
+    <t>COT200011</t>
+  </si>
+  <si>
+    <t>048111</t>
+  </si>
+  <si>
+    <t>COT200012</t>
+  </si>
+  <si>
+    <t>048112</t>
+  </si>
+  <si>
+    <t>COT200013</t>
+  </si>
+  <si>
+    <t>048113</t>
+  </si>
+  <si>
+    <t>COT200014</t>
+  </si>
+  <si>
+    <t>048114</t>
+  </si>
+  <si>
+    <t>COT200015</t>
+  </si>
+  <si>
+    <t>048115</t>
+  </si>
+  <si>
+    <t>COT200016</t>
+  </si>
+  <si>
+    <t>048116</t>
+  </si>
+  <si>
+    <t>COT200017</t>
+  </si>
+  <si>
+    <t>048117</t>
+  </si>
+  <si>
+    <t>COT200018</t>
+  </si>
+  <si>
+    <t>048118</t>
+  </si>
+  <si>
+    <t>COT200019</t>
+  </si>
+  <si>
+    <t>048119</t>
+  </si>
+  <si>
+    <t>COT200020</t>
+  </si>
+  <si>
+    <t>048120</t>
+  </si>
+  <si>
+    <t>COT200021</t>
+  </si>
+  <si>
+    <t>048121</t>
+  </si>
+  <si>
+    <t>COT200022</t>
+  </si>
+  <si>
+    <t>COT200023</t>
+  </si>
+  <si>
+    <t>COT200024</t>
+  </si>
+  <si>
+    <t>048124</t>
+  </si>
+  <si>
+    <t>048125</t>
+  </si>
+  <si>
+    <t>048126</t>
+  </si>
+  <si>
+    <t>COT200027</t>
+  </si>
+  <si>
+    <t>048127</t>
+  </si>
+  <si>
+    <t>COT200028</t>
+  </si>
+  <si>
+    <t>048128</t>
+  </si>
+  <si>
+    <t>COT200029</t>
+  </si>
+  <si>
+    <t>048129</t>
+  </si>
+  <si>
+    <t>048130</t>
+  </si>
+  <si>
+    <t>COT200031</t>
+  </si>
+  <si>
+    <t>048131</t>
+  </si>
+  <si>
+    <t>COT200032</t>
+  </si>
+  <si>
+    <t>048132</t>
+  </si>
+  <si>
+    <t>COT200033</t>
+  </si>
+  <si>
+    <t>048133</t>
+  </si>
+  <si>
+    <t>COT200034</t>
+  </si>
+  <si>
+    <t>048134</t>
+  </si>
+  <si>
+    <t>COT200035</t>
+  </si>
+  <si>
+    <t>048135</t>
+  </si>
+  <si>
+    <t>COT200036</t>
+  </si>
+  <si>
+    <t>048136</t>
+  </si>
+  <si>
+    <t>XPTO999</t>
+  </si>
+  <si>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>048137</t>
+  </si>
+  <si>
+    <t>048138</t>
+  </si>
+  <si>
+    <t>048139</t>
+  </si>
+  <si>
+    <t>048140</t>
+  </si>
+  <si>
+    <t>048141</t>
   </si>
   <si>
     <t>COT</t>
   </si>
   <si>
+    <t>COT200045</t>
+  </si>
+  <si>
+    <t>048142</t>
+  </si>
+  <si>
+    <t>COT200046</t>
+  </si>
+  <si>
+    <t>048143</t>
+  </si>
+  <si>
+    <t>COT200047</t>
+  </si>
+  <si>
+    <t>048144</t>
+  </si>
+  <si>
+    <t>COT200048</t>
+  </si>
+  <si>
+    <t>048145</t>
+  </si>
+  <si>
+    <t>COT200049</t>
+  </si>
+  <si>
+    <t>048146</t>
+  </si>
+  <si>
+    <t>COT200050</t>
+  </si>
+  <si>
+    <t>048147</t>
+  </si>
+  <si>
     <t>2025-08-10</t>
   </si>
   <si>
@@ -139,17 +388,101 @@
     <t>2025-09-30</t>
   </si>
   <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>2025-09-12</t>
+  </si>
+  <si>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-09-14</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
     <t>2025-08-16</t>
   </si>
   <si>
+    <t>2025-08-17</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-05</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>2025-08-21</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>2025-10-20</t>
+  </si>
+  <si>
+    <t>2025-11-15</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,21 +545,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -264,7 +589,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -298,7 +623,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -333,10 +657,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -509,14 +832,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D118"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,7 +850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -538,13 +858,13 @@
         <v>5000</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -552,13 +872,13 @@
         <v>7500</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -566,13 +886,13 @@
         <v>7500</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -580,13 +900,13 @@
         <v>10000</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -594,13 +914,13 @@
         <v>10000</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -608,13 +928,13 @@
         <v>8000</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -622,13 +942,13 @@
         <v>7000</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -636,13 +956,13 @@
         <v>10000</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -650,13 +970,13 @@
         <v>6000</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -664,13 +984,13 @@
         <v>6000</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -678,13 +998,13 @@
         <v>15000</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -692,13 +1012,13 @@
         <v>15000</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -706,13 +1026,13 @@
         <v>15000</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -720,13 +1040,13 @@
         <v>15000</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -734,13 +1054,13 @@
         <v>15000</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -748,13 +1068,13 @@
         <v>20000</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -762,13 +1082,13 @@
         <v>15000</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -776,13 +1096,13 @@
         <v>4000</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -790,13 +1110,13 @@
         <v>4000</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -804,13 +1124,13 @@
         <v>45000</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -818,38 +1138,1354 @@
         <v>45000</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>20</v>
       </c>
       <c r="B23">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>21</v>
       </c>
       <c r="B24">
+        <v>10000</v>
+      </c>
+      <c r="C24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>7500</v>
+      </c>
+      <c r="C25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>7500</v>
+      </c>
+      <c r="C26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>5000</v>
+      </c>
+      <c r="C27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>5000</v>
+      </c>
+      <c r="C28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>12500</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>12500</v>
+      </c>
+      <c r="C30" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>15000</v>
+      </c>
+      <c r="C31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>15000</v>
+      </c>
+      <c r="C32" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>25000</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34">
+        <v>25000</v>
+      </c>
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>7500</v>
+      </c>
+      <c r="C35" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>7500</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>10000</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>10000</v>
+      </c>
+      <c r="C38" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>12500</v>
+      </c>
+      <c r="C39" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40">
+        <v>12500</v>
+      </c>
+      <c r="C40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>9000</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>9000</v>
+      </c>
+      <c r="C42" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>6000</v>
+      </c>
+      <c r="C43" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>6000</v>
+      </c>
+      <c r="C44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>15000</v>
+      </c>
+      <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46">
+        <v>15000</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>15000</v>
+      </c>
+      <c r="C47" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>15000</v>
+      </c>
+      <c r="C48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>15000</v>
+      </c>
+      <c r="C49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>15000</v>
+      </c>
+      <c r="C50" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>10000</v>
+      </c>
+      <c r="C51" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52">
+        <v>10000</v>
+      </c>
+      <c r="C52" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>30000</v>
+      </c>
+      <c r="C53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>30000</v>
+      </c>
+      <c r="C54" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>19000</v>
+      </c>
+      <c r="C55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>19000</v>
+      </c>
+      <c r="C56" t="s">
+        <v>129</v>
+      </c>
+      <c r="D56" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>25000</v>
+      </c>
+      <c r="C57" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>25000</v>
+      </c>
+      <c r="C58" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>50000</v>
+      </c>
+      <c r="C59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>50000</v>
+      </c>
+      <c r="C60" t="s">
+        <v>138</v>
+      </c>
+      <c r="D60" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>15000</v>
+      </c>
+      <c r="C61" t="s">
+        <v>121</v>
+      </c>
+      <c r="D61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>15000</v>
+      </c>
+      <c r="C62" t="s">
+        <v>139</v>
+      </c>
+      <c r="D62" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>10000</v>
+      </c>
+      <c r="C63" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>5000</v>
+      </c>
+      <c r="C64" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65">
+        <v>5000</v>
+      </c>
+      <c r="C65" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66">
+        <v>20000</v>
+      </c>
+      <c r="C66" t="s">
+        <v>134</v>
+      </c>
+      <c r="D66" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67">
+        <v>5000</v>
+      </c>
+      <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>63</v>
+      </c>
+      <c r="B68">
+        <v>7000</v>
+      </c>
+      <c r="C68" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>63</v>
+      </c>
+      <c r="B69">
+        <v>8000</v>
+      </c>
+      <c r="C69" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <v>12500</v>
+      </c>
+      <c r="C70" t="s">
+        <v>113</v>
+      </c>
+      <c r="D70" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>65</v>
+      </c>
+      <c r="B71">
+        <v>12500</v>
+      </c>
+      <c r="C71" t="s">
+        <v>142</v>
+      </c>
+      <c r="D71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72">
+        <v>10000</v>
+      </c>
+      <c r="C72" t="s">
+        <v>113</v>
+      </c>
+      <c r="D72" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>66</v>
+      </c>
+      <c r="B73">
+        <v>10000</v>
+      </c>
+      <c r="C73" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74">
+        <v>10000</v>
+      </c>
+      <c r="C74" t="s">
+        <v>143</v>
+      </c>
+      <c r="D74" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75">
+        <v>10000</v>
+      </c>
+      <c r="C75" t="s">
+        <v>144</v>
+      </c>
+      <c r="D75" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76">
+        <v>10000</v>
+      </c>
+      <c r="C76" t="s">
+        <v>145</v>
+      </c>
+      <c r="D76" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77">
+        <v>25000</v>
+      </c>
+      <c r="C77" t="s">
+        <v>119</v>
+      </c>
+      <c r="D77" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78">
+        <v>10000</v>
+      </c>
+      <c r="C78" t="s">
+        <v>136</v>
+      </c>
+      <c r="D78" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B79">
+        <v>10000</v>
+      </c>
+      <c r="C79" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80">
+        <v>10000</v>
+      </c>
+      <c r="C80" t="s">
+        <v>146</v>
+      </c>
+      <c r="D80" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81">
+        <v>17500</v>
+      </c>
+      <c r="C81" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>71</v>
+      </c>
+      <c r="B82">
+        <v>17500</v>
+      </c>
+      <c r="C82" t="s">
+        <v>147</v>
+      </c>
+      <c r="D82" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83">
+        <v>10000</v>
+      </c>
+      <c r="C83" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>72</v>
+      </c>
+      <c r="B84">
+        <v>15000</v>
+      </c>
+      <c r="C84" t="s">
+        <v>131</v>
+      </c>
+      <c r="D84" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>73</v>
+      </c>
+      <c r="B85">
+        <v>15000</v>
+      </c>
+      <c r="C85" t="s">
+        <v>148</v>
+      </c>
+      <c r="D85" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B86">
+        <v>0.01</v>
+      </c>
+      <c r="C86" t="s">
+        <v>149</v>
+      </c>
+      <c r="D86" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87">
+        <v>12500</v>
+      </c>
+      <c r="C87" t="s">
+        <v>141</v>
+      </c>
+      <c r="D87" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>76</v>
+      </c>
+      <c r="B88">
+        <v>12500</v>
+      </c>
+      <c r="C88" t="s">
+        <v>133</v>
+      </c>
+      <c r="D88" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>77</v>
+      </c>
+      <c r="B89">
+        <v>4000</v>
+      </c>
+      <c r="C89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D89" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>78</v>
+      </c>
+      <c r="B90">
+        <v>4000</v>
+      </c>
+      <c r="C90" t="s">
+        <v>124</v>
+      </c>
+      <c r="D90" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>79</v>
+      </c>
+      <c r="B91">
+        <v>7500</v>
+      </c>
+      <c r="C91" t="s">
+        <v>143</v>
+      </c>
+      <c r="D91" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>80</v>
+      </c>
+      <c r="B92">
+        <v>7500</v>
+      </c>
+      <c r="C92" t="s">
+        <v>126</v>
+      </c>
+      <c r="D92" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>81</v>
+      </c>
+      <c r="B93">
+        <v>11500</v>
+      </c>
+      <c r="C93" t="s">
+        <v>115</v>
+      </c>
+      <c r="D93" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>82</v>
+      </c>
+      <c r="B94">
+        <v>11500</v>
+      </c>
+      <c r="C94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>83</v>
+      </c>
+      <c r="B95">
+        <v>9000</v>
+      </c>
+      <c r="C95" t="s">
+        <v>150</v>
+      </c>
+      <c r="D95" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>84</v>
+      </c>
+      <c r="B96">
+        <v>9000</v>
+      </c>
+      <c r="C96" t="s">
+        <v>129</v>
+      </c>
+      <c r="D96" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97">
+        <v>11000</v>
+      </c>
+      <c r="C97" t="s">
+        <v>144</v>
+      </c>
+      <c r="D97" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>86</v>
+      </c>
+      <c r="B98">
+        <v>11000</v>
+      </c>
+      <c r="C98" t="s">
+        <v>114</v>
+      </c>
+      <c r="D98" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>87</v>
+      </c>
+      <c r="B99">
+        <v>1000</v>
+      </c>
+      <c r="C99" t="s">
+        <v>113</v>
+      </c>
+      <c r="D99" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>88</v>
+      </c>
+      <c r="B100">
+        <v>2000</v>
+      </c>
+      <c r="C100" t="s">
+        <v>136</v>
+      </c>
+      <c r="D100" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>89</v>
+      </c>
+      <c r="B101">
+        <v>10000</v>
+      </c>
+      <c r="C101" t="s">
+        <v>119</v>
+      </c>
+      <c r="D101" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>90</v>
+      </c>
+      <c r="B102">
+        <v>-1000</v>
+      </c>
+      <c r="C102" t="s">
+        <v>149</v>
+      </c>
+      <c r="D102" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>91</v>
+      </c>
+      <c r="B103">
+        <v>8000</v>
+      </c>
+      <c r="C103" t="s">
+        <v>151</v>
+      </c>
+      <c r="D103" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>92</v>
+      </c>
+      <c r="B104">
+        <v>6000</v>
+      </c>
+      <c r="C104" t="s">
+        <v>122</v>
+      </c>
+      <c r="D104" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>93</v>
+      </c>
+      <c r="B105">
+        <v>12000</v>
+      </c>
+      <c r="C105" t="s">
+        <v>119</v>
+      </c>
+      <c r="D105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>94</v>
+      </c>
+      <c r="B106">
         <v>500</v>
       </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" t="s">
-        <v>40</v>
+      <c r="C106" t="s">
+        <v>136</v>
+      </c>
+      <c r="D106" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>95</v>
+      </c>
+      <c r="B107">
+        <v>9000</v>
+      </c>
+      <c r="C107" t="s">
+        <v>119</v>
+      </c>
+      <c r="D107" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>96</v>
+      </c>
+      <c r="B108">
+        <v>9000</v>
+      </c>
+      <c r="C108" t="s">
+        <v>133</v>
+      </c>
+      <c r="D108" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>97</v>
+      </c>
+      <c r="B109">
+        <v>11000</v>
+      </c>
+      <c r="C109" t="s">
+        <v>149</v>
+      </c>
+      <c r="D109" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>98</v>
+      </c>
+      <c r="B110">
+        <v>11000</v>
+      </c>
+      <c r="C110" t="s">
+        <v>124</v>
+      </c>
+      <c r="D110" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>99</v>
+      </c>
+      <c r="B111">
+        <v>15000</v>
+      </c>
+      <c r="C111" t="s">
+        <v>145</v>
+      </c>
+      <c r="D111" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>100</v>
+      </c>
+      <c r="B112">
+        <v>15000</v>
+      </c>
+      <c r="C112" t="s">
+        <v>126</v>
+      </c>
+      <c r="D112" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>101</v>
+      </c>
+      <c r="B113">
+        <v>17500</v>
+      </c>
+      <c r="C113" t="s">
+        <v>109</v>
+      </c>
+      <c r="D113" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>102</v>
+      </c>
+      <c r="B114">
+        <v>17500</v>
+      </c>
+      <c r="C114" t="s">
+        <v>128</v>
+      </c>
+      <c r="D114" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>103</v>
+      </c>
+      <c r="B115">
+        <v>14000</v>
+      </c>
+      <c r="C115" t="s">
+        <v>116</v>
+      </c>
+      <c r="D115" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>104</v>
+      </c>
+      <c r="B116">
+        <v>14000</v>
+      </c>
+      <c r="C116" t="s">
+        <v>129</v>
+      </c>
+      <c r="D116" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>105</v>
+      </c>
+      <c r="B117">
+        <v>25000</v>
+      </c>
+      <c r="C117" t="s">
+        <v>122</v>
+      </c>
+      <c r="D117" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>106</v>
+      </c>
+      <c r="B118">
+        <v>25000</v>
+      </c>
+      <c r="C118" t="s">
+        <v>114</v>
+      </c>
+      <c r="D118" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="119">
   <si>
     <t>Documento</t>
   </si>
@@ -67,10 +67,7 @@
     <t>048005</t>
   </si>
   <si>
-    <t>12345</t>
-  </si>
-  <si>
-    <t>COT100010</t>
+    <t>COT100009</t>
   </si>
   <si>
     <t>048008</t>
@@ -112,229 +109,136 @@
     <t>048106</t>
   </si>
   <si>
-    <t>COT200007</t>
-  </si>
-  <si>
     <t>048107</t>
   </si>
   <si>
-    <t>COT200008</t>
-  </si>
-  <si>
     <t>048108</t>
   </si>
   <si>
-    <t>COT200009</t>
-  </si>
-  <si>
     <t>048109</t>
   </si>
   <si>
-    <t>COT200010</t>
-  </si>
-  <si>
     <t>048110</t>
   </si>
   <si>
-    <t>COT200011</t>
-  </si>
-  <si>
     <t>048111</t>
   </si>
   <si>
-    <t>COT200012</t>
-  </si>
-  <si>
     <t>048112</t>
   </si>
   <si>
-    <t>COT200013</t>
-  </si>
-  <si>
-    <t>048113</t>
-  </si>
-  <si>
-    <t>COT200014</t>
-  </si>
-  <si>
-    <t>048114</t>
+    <t>048213</t>
+  </si>
+  <si>
+    <t>048214</t>
   </si>
   <si>
     <t>COT200015</t>
   </si>
   <si>
-    <t>048115</t>
-  </si>
-  <si>
-    <t>COT200016</t>
-  </si>
-  <si>
-    <t>048116</t>
-  </si>
-  <si>
-    <t>COT200017</t>
-  </si>
-  <si>
-    <t>048117</t>
+    <t>048216</t>
+  </si>
+  <si>
+    <t>048217</t>
   </si>
   <si>
     <t>COT200018</t>
   </si>
   <si>
-    <t>048118</t>
-  </si>
-  <si>
-    <t>COT200019</t>
-  </si>
-  <si>
-    <t>048119</t>
-  </si>
-  <si>
-    <t>COT200020</t>
-  </si>
-  <si>
-    <t>048120</t>
+    <t>048219</t>
+  </si>
+  <si>
+    <t>048220</t>
   </si>
   <si>
     <t>COT200021</t>
   </si>
   <si>
-    <t>048121</t>
-  </si>
-  <si>
-    <t>COT200022</t>
-  </si>
-  <si>
-    <t>COT200023</t>
+    <t>048222</t>
+  </si>
+  <si>
+    <t>048223</t>
   </si>
   <si>
     <t>COT200024</t>
   </si>
   <si>
-    <t>048124</t>
-  </si>
-  <si>
-    <t>048125</t>
-  </si>
-  <si>
-    <t>048126</t>
+    <t>048225</t>
+  </si>
+  <si>
+    <t>048226</t>
   </si>
   <si>
     <t>COT200027</t>
   </si>
   <si>
-    <t>048127</t>
-  </si>
-  <si>
-    <t>COT200028</t>
-  </si>
-  <si>
-    <t>048128</t>
-  </si>
-  <si>
-    <t>COT200029</t>
-  </si>
-  <si>
-    <t>048129</t>
-  </si>
-  <si>
-    <t>048130</t>
-  </si>
-  <si>
-    <t>COT200031</t>
-  </si>
-  <si>
-    <t>048131</t>
-  </si>
-  <si>
-    <t>COT200032</t>
-  </si>
-  <si>
-    <t>048132</t>
+    <t>048228</t>
+  </si>
+  <si>
+    <t>048229</t>
+  </si>
+  <si>
+    <t>COT200030</t>
+  </si>
+  <si>
+    <t>048231</t>
+  </si>
+  <si>
+    <t>048232</t>
   </si>
   <si>
     <t>COT200033</t>
   </si>
   <si>
-    <t>048133</t>
-  </si>
-  <si>
-    <t>COT200034</t>
-  </si>
-  <si>
-    <t>048134</t>
-  </si>
-  <si>
-    <t>COT200035</t>
-  </si>
-  <si>
-    <t>048135</t>
+    <t>048234</t>
+  </si>
+  <si>
+    <t>048235</t>
   </si>
   <si>
     <t>COT200036</t>
   </si>
   <si>
-    <t>048136</t>
-  </si>
-  <si>
-    <t>XPTO999</t>
-  </si>
-  <si>
-    <t>999999</t>
-  </si>
-  <si>
-    <t>048137</t>
-  </si>
-  <si>
-    <t>048138</t>
-  </si>
-  <si>
-    <t>048139</t>
-  </si>
-  <si>
-    <t>048140</t>
-  </si>
-  <si>
-    <t>048141</t>
-  </si>
-  <si>
-    <t>COT</t>
+    <t>048237</t>
+  </si>
+  <si>
+    <t>048238</t>
+  </si>
+  <si>
+    <t>COT200039</t>
+  </si>
+  <si>
+    <t>048240</t>
+  </si>
+  <si>
+    <t>048241</t>
+  </si>
+  <si>
+    <t>COT200042</t>
+  </si>
+  <si>
+    <t>048243</t>
+  </si>
+  <si>
+    <t>048244</t>
   </si>
   <si>
     <t>COT200045</t>
   </si>
   <si>
-    <t>048142</t>
-  </si>
-  <si>
-    <t>COT200046</t>
-  </si>
-  <si>
-    <t>048143</t>
-  </si>
-  <si>
-    <t>COT200047</t>
-  </si>
-  <si>
-    <t>048144</t>
+    <t>048246</t>
+  </si>
+  <si>
+    <t>048247</t>
   </si>
   <si>
     <t>COT200048</t>
   </si>
   <si>
-    <t>048145</t>
-  </si>
-  <si>
-    <t>COT200049</t>
-  </si>
-  <si>
-    <t>048146</t>
-  </si>
-  <si>
-    <t>COT200050</t>
-  </si>
-  <si>
-    <t>048147</t>
+    <t>048249</t>
+  </si>
+  <si>
+    <t>048250</t>
   </si>
   <si>
     <t>2025-08-10</t>
@@ -382,12 +286,57 @@
     <t>2025-08-18</t>
   </si>
   <si>
-    <t>2025-08-30</t>
-  </si>
-  <si>
     <t>2025-09-30</t>
   </si>
   <si>
+    <t>2025-08-6</t>
+  </si>
+  <si>
+    <t>2025-09-16</t>
+  </si>
+  <si>
+    <t>2025-08-7</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>2025-08-8</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>2025-08-9</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>2025-08-23</t>
+  </si>
+  <si>
     <t>2025-09-10</t>
   </si>
   <si>
@@ -397,85 +346,31 @@
     <t>2025-09-12</t>
   </si>
   <si>
+    <t>2025-09-13</t>
+  </si>
+  <si>
+    <t>2025-08-09</t>
+  </si>
+  <si>
+    <t>2025-08-21</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>2025-09-11</t>
+  </si>
+  <si>
     <t>2025-08-07</t>
   </si>
   <si>
     <t>2025-09-14</t>
   </si>
   <si>
-    <t>2025-09-16</t>
-  </si>
-  <si>
-    <t>2025-08-09</t>
-  </si>
-  <si>
-    <t>2025-09-18</t>
-  </si>
-  <si>
-    <t>2025-08-11</t>
-  </si>
-  <si>
-    <t>2025-09-08</t>
-  </si>
-  <si>
     <t>2025-08-13</t>
   </si>
   <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
-    <t>2025-08-16</t>
-  </si>
-  <si>
-    <t>2025-08-17</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>2025-09-24</t>
-  </si>
-  <si>
-    <t>2025-09-05</t>
-  </si>
-  <si>
-    <t>2025-08-19</t>
-  </si>
-  <si>
-    <t>2025-10-15</t>
-  </si>
-  <si>
-    <t>2025-08-21</t>
-  </si>
-  <si>
-    <t>2025-08-24</t>
-  </si>
-  <si>
-    <t>2025-08-27</t>
-  </si>
-  <si>
-    <t>2025-10-20</t>
-  </si>
-  <si>
-    <t>2025-11-15</t>
-  </si>
-  <si>
-    <t>2025-10-10</t>
-  </si>
-  <si>
-    <t>2025-08-26</t>
-  </si>
-  <si>
-    <t>2025-08-23</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
 </sst>
 </file>
@@ -833,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -858,10 +753,10 @@
         <v>5000</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -872,10 +767,10 @@
         <v>7500</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -886,10 +781,10 @@
         <v>7500</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -900,10 +795,10 @@
         <v>10000</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -914,10 +809,10 @@
         <v>10000</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -928,10 +823,10 @@
         <v>8000</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -942,10 +837,10 @@
         <v>7000</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -956,10 +851,10 @@
         <v>10000</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -970,10 +865,10 @@
         <v>6000</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -984,10 +879,10 @@
         <v>6000</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -998,10 +893,10 @@
         <v>15000</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1012,10 +907,10 @@
         <v>15000</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1026,10 +921,10 @@
         <v>15000</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1040,10 +935,10 @@
         <v>15000</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1054,10 +949,10 @@
         <v>15000</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1068,10 +963,10 @@
         <v>20000</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1082,10 +977,10 @@
         <v>15000</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1096,1396 +991,808 @@
         <v>4000</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21">
-        <v>45000</v>
+        <v>7500</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>45000</v>
+        <v>7500</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>7500</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>7500</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30">
-        <v>12500</v>
+        <v>7500</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32">
-        <v>15000</v>
+        <v>7500</v>
       </c>
       <c r="C32" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="C38" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39">
-        <v>12500</v>
+        <v>13300</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40">
-        <v>12500</v>
+        <v>13400</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D40" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41">
-        <v>9000</v>
+        <v>6750</v>
       </c>
       <c r="C41" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42">
-        <v>9000</v>
+        <v>13600</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D42" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43">
-        <v>6000</v>
+        <v>13700</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44">
-        <v>6000</v>
+        <v>6900</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45">
-        <v>15000</v>
+        <v>13900</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47">
-        <v>15000</v>
+        <v>7050</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48">
-        <v>15000</v>
+        <v>14200</v>
       </c>
       <c r="C48" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49">
-        <v>15000</v>
+        <v>14300</v>
       </c>
       <c r="C49" t="s">
         <v>110</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B50">
-        <v>15000</v>
+        <v>7200</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51">
-        <v>10000</v>
+        <v>14500</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52">
-        <v>10000</v>
+        <v>14600</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53">
-        <v>30000</v>
+        <v>7350</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="D53" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54">
-        <v>30000</v>
+        <v>14800</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55">
-        <v>19000</v>
+        <v>14900</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56">
-        <v>19000</v>
+        <v>7500</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57">
-        <v>25000</v>
+        <v>15100</v>
       </c>
       <c r="C57" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B58">
-        <v>25000</v>
+        <v>15200</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59">
-        <v>50000</v>
+        <v>7650</v>
       </c>
       <c r="C59" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60">
-        <v>50000</v>
+        <v>15400</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61">
-        <v>15000</v>
+        <v>15500</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62">
-        <v>15000</v>
+        <v>7800</v>
       </c>
       <c r="C62" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63">
-        <v>10000</v>
+        <v>15700</v>
       </c>
       <c r="C63" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64">
-        <v>5000</v>
+        <v>15800</v>
       </c>
       <c r="C64" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B65">
-        <v>5000</v>
+        <v>7950</v>
       </c>
       <c r="C65" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B66">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="D66" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B67">
-        <v>5000</v>
+        <v>16100</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D67" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B68">
-        <v>7000</v>
+        <v>8100</v>
       </c>
       <c r="C68" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D68" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B69">
-        <v>8000</v>
+        <v>16300</v>
       </c>
       <c r="C69" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="D69" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B70">
-        <v>12500</v>
+        <v>16400</v>
       </c>
       <c r="C70" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B71">
-        <v>12500</v>
+        <v>8250</v>
       </c>
       <c r="C71" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="D71" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B72">
-        <v>10000</v>
+        <v>16600</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="D72" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B73">
-        <v>10000</v>
+        <v>16700</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="D73" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B74">
-        <v>10000</v>
+        <v>8400</v>
       </c>
       <c r="C74" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B75">
-        <v>10000</v>
+        <v>16900</v>
       </c>
       <c r="C75" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B76">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="C76" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="D76" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77">
-        <v>25000</v>
-      </c>
-      <c r="C77" t="s">
-        <v>119</v>
-      </c>
-      <c r="D77" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78">
-        <v>10000</v>
-      </c>
-      <c r="C78" t="s">
-        <v>136</v>
-      </c>
-      <c r="D78" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>69</v>
-      </c>
-      <c r="B79">
-        <v>10000</v>
-      </c>
-      <c r="C79" t="s">
-        <v>114</v>
-      </c>
-      <c r="D79" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>69</v>
-      </c>
-      <c r="B80">
-        <v>10000</v>
-      </c>
-      <c r="C80" t="s">
-        <v>146</v>
-      </c>
-      <c r="D80" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>70</v>
-      </c>
-      <c r="B81">
-        <v>17500</v>
-      </c>
-      <c r="C81" t="s">
-        <v>137</v>
-      </c>
-      <c r="D81" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>71</v>
-      </c>
-      <c r="B82">
-        <v>17500</v>
-      </c>
-      <c r="C82" t="s">
-        <v>147</v>
-      </c>
-      <c r="D82" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>72</v>
-      </c>
-      <c r="B83">
-        <v>10000</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
-        <v>72</v>
-      </c>
-      <c r="B84">
-        <v>15000</v>
-      </c>
-      <c r="C84" t="s">
-        <v>131</v>
-      </c>
-      <c r="D84" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
-        <v>73</v>
-      </c>
-      <c r="B85">
-        <v>15000</v>
-      </c>
-      <c r="C85" t="s">
-        <v>148</v>
-      </c>
-      <c r="D85" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
-        <v>74</v>
-      </c>
-      <c r="B86">
-        <v>0.01</v>
-      </c>
-      <c r="C86" t="s">
-        <v>149</v>
-      </c>
-      <c r="D86" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
-        <v>75</v>
-      </c>
-      <c r="B87">
-        <v>12500</v>
-      </c>
-      <c r="C87" t="s">
-        <v>141</v>
-      </c>
-      <c r="D87" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>76</v>
-      </c>
-      <c r="B88">
-        <v>12500</v>
-      </c>
-      <c r="C88" t="s">
-        <v>133</v>
-      </c>
-      <c r="D88" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>77</v>
-      </c>
-      <c r="B89">
-        <v>4000</v>
-      </c>
-      <c r="C89" t="s">
-        <v>117</v>
-      </c>
-      <c r="D89" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>78</v>
-      </c>
-      <c r="B90">
-        <v>4000</v>
-      </c>
-      <c r="C90" t="s">
-        <v>124</v>
-      </c>
-      <c r="D90" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
-        <v>79</v>
-      </c>
-      <c r="B91">
-        <v>7500</v>
-      </c>
-      <c r="C91" t="s">
-        <v>143</v>
-      </c>
-      <c r="D91" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
-        <v>80</v>
-      </c>
-      <c r="B92">
-        <v>7500</v>
-      </c>
-      <c r="C92" t="s">
-        <v>126</v>
-      </c>
-      <c r="D92" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>81</v>
-      </c>
-      <c r="B93">
-        <v>11500</v>
-      </c>
-      <c r="C93" t="s">
-        <v>115</v>
-      </c>
-      <c r="D93" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
-        <v>82</v>
-      </c>
-      <c r="B94">
-        <v>11500</v>
-      </c>
-      <c r="C94" t="s">
-        <v>128</v>
-      </c>
-      <c r="D94" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95">
-        <v>9000</v>
-      </c>
-      <c r="C95" t="s">
-        <v>150</v>
-      </c>
-      <c r="D95" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
-        <v>84</v>
-      </c>
-      <c r="B96">
-        <v>9000</v>
-      </c>
-      <c r="C96" t="s">
-        <v>129</v>
-      </c>
-      <c r="D96" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>85</v>
-      </c>
-      <c r="B97">
-        <v>11000</v>
-      </c>
-      <c r="C97" t="s">
-        <v>144</v>
-      </c>
-      <c r="D97" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" t="s">
-        <v>86</v>
-      </c>
-      <c r="B98">
-        <v>11000</v>
-      </c>
-      <c r="C98" t="s">
-        <v>114</v>
-      </c>
-      <c r="D98" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>87</v>
-      </c>
-      <c r="B99">
-        <v>1000</v>
-      </c>
-      <c r="C99" t="s">
-        <v>113</v>
-      </c>
-      <c r="D99" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
-        <v>88</v>
-      </c>
-      <c r="B100">
-        <v>2000</v>
-      </c>
-      <c r="C100" t="s">
-        <v>136</v>
-      </c>
-      <c r="D100" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" t="s">
-        <v>89</v>
-      </c>
-      <c r="B101">
-        <v>10000</v>
-      </c>
-      <c r="C101" t="s">
-        <v>119</v>
-      </c>
-      <c r="D101" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" t="s">
-        <v>90</v>
-      </c>
-      <c r="B102">
-        <v>-1000</v>
-      </c>
-      <c r="C102" t="s">
-        <v>149</v>
-      </c>
-      <c r="D102" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" t="s">
-        <v>91</v>
-      </c>
-      <c r="B103">
-        <v>8000</v>
-      </c>
-      <c r="C103" t="s">
-        <v>151</v>
-      </c>
-      <c r="D103" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" t="s">
-        <v>92</v>
-      </c>
-      <c r="B104">
-        <v>6000</v>
-      </c>
-      <c r="C104" t="s">
-        <v>122</v>
-      </c>
-      <c r="D104" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" t="s">
-        <v>93</v>
-      </c>
-      <c r="B105">
-        <v>12000</v>
-      </c>
-      <c r="C105" t="s">
-        <v>119</v>
-      </c>
-      <c r="D105" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" t="s">
-        <v>94</v>
-      </c>
-      <c r="B106">
-        <v>500</v>
-      </c>
-      <c r="C106" t="s">
-        <v>136</v>
-      </c>
-      <c r="D106" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" t="s">
-        <v>95</v>
-      </c>
-      <c r="B107">
-        <v>9000</v>
-      </c>
-      <c r="C107" t="s">
-        <v>119</v>
-      </c>
-      <c r="D107" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" t="s">
-        <v>96</v>
-      </c>
-      <c r="B108">
-        <v>9000</v>
-      </c>
-      <c r="C108" t="s">
-        <v>133</v>
-      </c>
-      <c r="D108" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" t="s">
-        <v>97</v>
-      </c>
-      <c r="B109">
-        <v>11000</v>
-      </c>
-      <c r="C109" t="s">
-        <v>149</v>
-      </c>
-      <c r="D109" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" t="s">
-        <v>98</v>
-      </c>
-      <c r="B110">
-        <v>11000</v>
-      </c>
-      <c r="C110" t="s">
-        <v>124</v>
-      </c>
-      <c r="D110" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" t="s">
-        <v>99</v>
-      </c>
-      <c r="B111">
-        <v>15000</v>
-      </c>
-      <c r="C111" t="s">
-        <v>145</v>
-      </c>
-      <c r="D111" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" t="s">
-        <v>100</v>
-      </c>
-      <c r="B112">
-        <v>15000</v>
-      </c>
-      <c r="C112" t="s">
-        <v>126</v>
-      </c>
-      <c r="D112" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" t="s">
-        <v>101</v>
-      </c>
-      <c r="B113">
-        <v>17500</v>
-      </c>
-      <c r="C113" t="s">
-        <v>109</v>
-      </c>
-      <c r="D113" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" t="s">
-        <v>102</v>
-      </c>
-      <c r="B114">
-        <v>17500</v>
-      </c>
-      <c r="C114" t="s">
-        <v>128</v>
-      </c>
-      <c r="D114" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" t="s">
-        <v>103</v>
-      </c>
-      <c r="B115">
-        <v>14000</v>
-      </c>
-      <c r="C115" t="s">
-        <v>116</v>
-      </c>
-      <c r="D115" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" t="s">
-        <v>104</v>
-      </c>
-      <c r="B116">
-        <v>14000</v>
-      </c>
-      <c r="C116" t="s">
-        <v>129</v>
-      </c>
-      <c r="D116" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" t="s">
-        <v>105</v>
-      </c>
-      <c r="B117">
-        <v>25000</v>
-      </c>
-      <c r="C117" t="s">
-        <v>122</v>
-      </c>
-      <c r="D117" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" t="s">
-        <v>106</v>
-      </c>
-      <c r="B118">
-        <v>25000</v>
-      </c>
-      <c r="C118" t="s">
-        <v>114</v>
-      </c>
-      <c r="D118" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -750,7 +750,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
@@ -764,7 +764,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="C3" t="s">
         <v>76</v>
@@ -778,7 +778,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="C4" t="s">
         <v>77</v>
@@ -792,7 +792,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>40000</v>
+        <v>7500</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -806,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>40000</v>
+        <v>7500</v>
       </c>
       <c r="C6" t="s">
         <v>79</v>
@@ -820,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>32000</v>
+        <v>6000</v>
       </c>
       <c r="C7" t="s">
         <v>80</v>
@@ -834,7 +834,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
@@ -848,7 +848,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="C9" t="s">
         <v>82</v>
@@ -862,7 +862,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
@@ -876,7 +876,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="C11" t="s">
         <v>84</v>
@@ -890,7 +890,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>60000</v>
+        <v>11000</v>
       </c>
       <c r="C12" t="s">
         <v>85</v>
@@ -904,7 +904,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>60000</v>
+        <v>11000</v>
       </c>
       <c r="C13" t="s">
         <v>86</v>
@@ -918,7 +918,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>60000</v>
+        <v>52500</v>
       </c>
       <c r="C14" t="s">
         <v>87</v>
@@ -932,7 +932,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>60000</v>
+        <v>52500</v>
       </c>
       <c r="C15" t="s">
         <v>88</v>
@@ -946,7 +946,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>45000</v>
+        <v>5000</v>
       </c>
       <c r="C16" t="s">
         <v>89</v>
@@ -960,7 +960,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>60000</v>
+        <v>6000</v>
       </c>
       <c r="C17" t="s">
         <v>83</v>
@@ -974,7 +974,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>45000</v>
+        <v>5000</v>
       </c>
       <c r="C18" t="s">
         <v>77</v>
@@ -988,7 +988,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="C19" t="s">
         <v>89</v>
@@ -1002,7 +1002,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="C20" t="s">
         <v>90</v>
@@ -1016,7 +1016,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>32500</v>
+        <v>7000</v>
       </c>
       <c r="C21" t="s">
         <v>91</v>
@@ -1030,7 +1030,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>32500</v>
+        <v>7000</v>
       </c>
       <c r="C22" t="s">
         <v>92</v>
@@ -1044,7 +1044,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="C23" t="s">
         <v>93</v>
@@ -1058,7 +1058,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="C24" t="s">
         <v>94</v>
@@ -1072,7 +1072,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>37500</v>
+        <v>9000</v>
       </c>
       <c r="C25" t="s">
         <v>95</v>
@@ -1086,7 +1086,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>37500</v>
+        <v>9000</v>
       </c>
       <c r="C26" t="s">
         <v>96</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="C27" t="s">
         <v>97</v>
@@ -1114,7 +1114,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="C28" t="s">
         <v>98</v>
@@ -1128,7 +1128,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>42500</v>
+        <v>11000</v>
       </c>
       <c r="C29" t="s">
         <v>75</v>
@@ -1142,7 +1142,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>42500</v>
+        <v>11000</v>
       </c>
       <c r="C30" t="s">
         <v>82</v>
@@ -1156,7 +1156,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="C31" t="s">
         <v>99</v>
@@ -1170,7 +1170,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="C32" t="s">
         <v>100</v>
@@ -1184,7 +1184,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>80000</v>
+        <v>14000</v>
       </c>
       <c r="C33" t="s">
         <v>94</v>
@@ -1198,7 +1198,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>90000</v>
+        <v>16000</v>
       </c>
       <c r="C34" t="s">
         <v>96</v>
@@ -1212,7 +1212,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>100000</v>
+        <v>18000</v>
       </c>
       <c r="C35" t="s">
         <v>98</v>
@@ -1226,7 +1226,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>110000</v>
+        <v>20000</v>
       </c>
       <c r="C36" t="s">
         <v>82</v>
@@ -1240,7 +1240,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>120000</v>
+        <v>22000</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
@@ -1254,7 +1254,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>130000</v>
+        <v>105000</v>
       </c>
       <c r="C38" t="s">
         <v>101</v>
@@ -1268,7 +1268,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>38000</v>
+        <v>5000</v>
       </c>
       <c r="C39" t="s">
         <v>102</v>
@@ -1282,7 +1282,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>39000</v>
+        <v>5300</v>
       </c>
       <c r="C40" t="s">
         <v>103</v>
@@ -1296,7 +1296,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>20000</v>
+        <v>2800</v>
       </c>
       <c r="C41" t="s">
         <v>85</v>
@@ -1310,7 +1310,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>41000</v>
+        <v>5900</v>
       </c>
       <c r="C42" t="s">
         <v>104</v>
@@ -1324,7 +1324,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>42000</v>
+        <v>6200</v>
       </c>
       <c r="C43" t="s">
         <v>105</v>
@@ -1338,7 +1338,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>21500</v>
+        <v>3250</v>
       </c>
       <c r="C44" t="s">
         <v>106</v>
@@ -1352,7 +1352,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>44000</v>
+        <v>6800</v>
       </c>
       <c r="C45" t="s">
         <v>88</v>
@@ -1366,7 +1366,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>45000</v>
+        <v>7100</v>
       </c>
       <c r="C46" t="s">
         <v>107</v>
@@ -1380,7 +1380,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>23000</v>
+        <v>3700</v>
       </c>
       <c r="C47" t="s">
         <v>108</v>
@@ -1394,7 +1394,7 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>47000</v>
+        <v>7700</v>
       </c>
       <c r="C48" t="s">
         <v>109</v>
@@ -1408,7 +1408,7 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>48000</v>
+        <v>8000</v>
       </c>
       <c r="C49" t="s">
         <v>110</v>
@@ -1422,7 +1422,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>24500</v>
+        <v>4150</v>
       </c>
       <c r="C50" t="s">
         <v>111</v>
@@ -1436,7 +1436,7 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>50000</v>
+        <v>8600</v>
       </c>
       <c r="C51" t="s">
         <v>79</v>
@@ -1450,7 +1450,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>51000</v>
+        <v>8900</v>
       </c>
       <c r="C52" t="s">
         <v>92</v>
@@ -1464,7 +1464,7 @@
         <v>51</v>
       </c>
       <c r="B53">
-        <v>26000</v>
+        <v>4600</v>
       </c>
       <c r="C53" t="s">
         <v>78</v>
@@ -1478,7 +1478,7 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>53000</v>
+        <v>9500</v>
       </c>
       <c r="C54" t="s">
         <v>96</v>
@@ -1492,7 +1492,7 @@
         <v>53</v>
       </c>
       <c r="B55">
-        <v>54000</v>
+        <v>9800</v>
       </c>
       <c r="C55" t="s">
         <v>98</v>
@@ -1506,7 +1506,7 @@
         <v>54</v>
       </c>
       <c r="B56">
-        <v>27500</v>
+        <v>5050</v>
       </c>
       <c r="C56" t="s">
         <v>81</v>
@@ -1520,7 +1520,7 @@
         <v>55</v>
       </c>
       <c r="B57">
-        <v>56000</v>
+        <v>10400</v>
       </c>
       <c r="C57" t="s">
         <v>100</v>
@@ -1534,7 +1534,7 @@
         <v>56</v>
       </c>
       <c r="B58">
-        <v>57000</v>
+        <v>10700</v>
       </c>
       <c r="C58" t="s">
         <v>101</v>
@@ -1548,7 +1548,7 @@
         <v>57</v>
       </c>
       <c r="B59">
-        <v>29000</v>
+        <v>5500</v>
       </c>
       <c r="C59" t="s">
         <v>89</v>
@@ -1562,7 +1562,7 @@
         <v>58</v>
       </c>
       <c r="B60">
-        <v>59000</v>
+        <v>11300</v>
       </c>
       <c r="C60" t="s">
         <v>103</v>
@@ -1576,7 +1576,7 @@
         <v>59</v>
       </c>
       <c r="B61">
-        <v>60000</v>
+        <v>11600</v>
       </c>
       <c r="C61" t="s">
         <v>86</v>
@@ -1590,7 +1590,7 @@
         <v>60</v>
       </c>
       <c r="B62">
-        <v>30500</v>
+        <v>5950</v>
       </c>
       <c r="C62" t="s">
         <v>112</v>
@@ -1604,7 +1604,7 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>62000</v>
+        <v>12200</v>
       </c>
       <c r="C63" t="s">
         <v>105</v>
@@ -1618,7 +1618,7 @@
         <v>62</v>
       </c>
       <c r="B64">
-        <v>63000</v>
+        <v>12500</v>
       </c>
       <c r="C64" t="s">
         <v>88</v>
@@ -1632,7 +1632,7 @@
         <v>63</v>
       </c>
       <c r="B65">
-        <v>32000</v>
+        <v>6400</v>
       </c>
       <c r="C65" t="s">
         <v>113</v>
@@ -1646,7 +1646,7 @@
         <v>64</v>
       </c>
       <c r="B66">
-        <v>65000</v>
+        <v>13100</v>
       </c>
       <c r="C66" t="s">
         <v>107</v>
@@ -1660,7 +1660,7 @@
         <v>65</v>
       </c>
       <c r="B67">
-        <v>66000</v>
+        <v>13400</v>
       </c>
       <c r="C67" t="s">
         <v>114</v>
@@ -1674,7 +1674,7 @@
         <v>66</v>
       </c>
       <c r="B68">
-        <v>33500</v>
+        <v>6850</v>
       </c>
       <c r="C68" t="s">
         <v>115</v>
@@ -1688,7 +1688,7 @@
         <v>67</v>
       </c>
       <c r="B69">
-        <v>68000</v>
+        <v>14000</v>
       </c>
       <c r="C69" t="s">
         <v>110</v>
@@ -1702,7 +1702,7 @@
         <v>68</v>
       </c>
       <c r="B70">
-        <v>69000</v>
+        <v>14300</v>
       </c>
       <c r="C70" t="s">
         <v>116</v>
@@ -1716,7 +1716,7 @@
         <v>69</v>
       </c>
       <c r="B71">
-        <v>35000</v>
+        <v>7300</v>
       </c>
       <c r="C71" t="s">
         <v>75</v>
@@ -1730,7 +1730,7 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>71000</v>
+        <v>14900</v>
       </c>
       <c r="C72" t="s">
         <v>92</v>
@@ -1744,7 +1744,7 @@
         <v>71</v>
       </c>
       <c r="B73">
-        <v>72000</v>
+        <v>15200</v>
       </c>
       <c r="C73" t="s">
         <v>94</v>
@@ -1758,7 +1758,7 @@
         <v>72</v>
       </c>
       <c r="B74">
-        <v>36500</v>
+        <v>7750</v>
       </c>
       <c r="C74" t="s">
         <v>117</v>
@@ -1772,7 +1772,7 @@
         <v>73</v>
       </c>
       <c r="B75">
-        <v>74000</v>
+        <v>15800</v>
       </c>
       <c r="C75" t="s">
         <v>98</v>
@@ -1786,7 +1786,7 @@
         <v>74</v>
       </c>
       <c r="B76">
-        <v>75000</v>
+        <v>16100</v>
       </c>
       <c r="C76" t="s">
         <v>82</v>

--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FA23250-7D9B-4133-8E16-F2CB66F67A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B21C4A-ADCB-436C-B13E-E82DFECD7632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Documento</t>
   </si>
@@ -46,6 +46,15 @@
   </si>
   <si>
     <t>Tipo de Baixa</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>048001</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
   </si>
 </sst>
 </file>
@@ -104,11 +113,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B145032-219E-4180-ABE3-1526A0324BEF}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -446,6 +456,34 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>48002</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45910</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B21C4A-ADCB-436C-B13E-E82DFECD7632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328C4236-DD81-448A-B5BA-28CE5784BE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328C4236-DD81-448A-B5BA-28CE5784BE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6343A869-51AF-4351-B842-0933191E2D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>Documento</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>048001</t>
-  </si>
-  <si>
-    <t>2025-08-28</t>
   </si>
 </sst>
 </file>
@@ -464,7 +461,7 @@
         <v>20</v>
       </c>
       <c r="C2" s="2">
-        <v>45910</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -477,8 +474,8 @@
       <c r="B3">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="C3" s="2">
+        <v>45866</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>

--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6343A869-51AF-4351-B842-0933191E2D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E01922-11F5-4283-9206-20D418A505BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/dados_entrada/Análise Financeira.xlsx
+++ b/dados_entrada/Análise Financeira.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E01922-11F5-4283-9206-20D418A505BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C381C8E-164D-41E0-9637-0CB6398AE71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F12AB9B-49F6-4BAE-BA61-A3C429BE1973}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>Documento</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>048001</t>
   </si>
 </sst>
 </file>
@@ -455,27 +452,27 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>48002</v>
+        <v>999001</v>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2">
-        <v>45879</v>
+        <v>45945</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
+      <c r="A3">
+        <v>999002</v>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2">
-        <v>45866</v>
+        <v>45950</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
